--- a/ig/nriss-patch-1/StructureDefinition-as-ext-practitionerrole-hascas.xlsx
+++ b/ig/nriss-patch-1/StructureDefinition-as-ext-practitionerrole-hascas.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-10T15:57:11+00:00</t>
+    <t>2023-07-11T12:03:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
